--- a/content/xls/indicators_01.07.2025.xlsx
+++ b/content/xls/indicators_01.07.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F8DF1D-8CF0-49E1-9A06-61A2178EC348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299E9678-2282-40A0-B2E5-905B2379FC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3052" yWindow="3052" windowWidth="23631" windowHeight="12542" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5994" yWindow="8554" windowWidth="23631" windowHeight="8566" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -184,9 +184,6 @@
     <t>80.9%</t>
   </si>
   <si>
-    <t>16.3%</t>
-  </si>
-  <si>
     <t>539 ед.</t>
   </si>
   <si>
@@ -253,6 +250,100 @@
     <r>
       <rPr>
         <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">↑ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ед. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.01.2025</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">↑ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ед. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.01.2025</t>
+    </r>
+  </si>
+  <si>
+    <t>210 ед.</t>
+  </si>
+  <si>
+    <t>16.5%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -269,7 +360,7 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 7 </t>
+      <t xml:space="preserve"> 11 </t>
     </r>
     <r>
       <rPr>
@@ -292,109 +383,26 @@
       </rPr>
       <t>к 01.01.2025</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">↑ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ед. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.01.2025</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">↑ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>19</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ед. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.01.2025</t>
-    </r>
-  </si>
-  <si>
-    <t>210 ед.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -492,21 +500,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -840,16 +851,16 @@
         <v>17</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>5</v>
@@ -863,22 +874,22 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>23</v>
+      <c r="C3" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>9</v>

--- a/content/xls/indicators_01.07.2025.xlsx
+++ b/content/xls/indicators_01.07.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299E9678-2282-40A0-B2E5-905B2379FC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFAEB8D-DC02-48C2-B7EF-7BB803A6D300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5994" yWindow="8554" windowWidth="23631" windowHeight="8566" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3791" yWindow="7471" windowWidth="23631" windowHeight="8566" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,6 @@
     <t>Уровень финансовой доступности</t>
   </si>
   <si>
-    <t>Присутствие банков</t>
-  </si>
-  <si>
-    <t>Присутствие Отделений почтовой связи</t>
-  </si>
-  <si>
     <t>2 ед.</t>
   </si>
   <si>
@@ -169,18 +163,6 @@
 дистанционного банковского обслуживания</t>
   </si>
   <si>
-    <t>Присутствие банкоматов</t>
-  </si>
-  <si>
-    <t>Присутствие торговых точек с сервисом «Выдача наличных на кассе»</t>
-  </si>
-  <si>
-    <t>Присутствие точек финансового доступа</t>
-  </si>
-  <si>
-    <t>Присутствие финансовых помощников</t>
-  </si>
-  <si>
     <t>80.9%</t>
   </si>
   <si>
@@ -204,13 +186,23 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">3.0 п.п. </t>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ед. </t>
     </r>
     <r>
       <rPr>
@@ -227,6 +219,108 @@
     <r>
       <rPr>
         <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">↑ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ед. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.01.2025</t>
+    </r>
+  </si>
+  <si>
+    <t>210 ед.</t>
+  </si>
+  <si>
+    <t>16.5%</t>
+  </si>
+  <si>
+    <t>Количество банков</t>
+  </si>
+  <si>
+    <t>Количество Отделений почтовой связи</t>
+  </si>
+  <si>
+    <t>Количество банкоматов</t>
+  </si>
+  <si>
+    <t>Количество торговых точек с сервисом «Выдача наличных на кассе»</t>
+  </si>
+  <si>
+    <t>Количество точек финансового доступа</t>
+  </si>
+  <si>
+    <t>Количество финансовых помощников</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">↑ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">3.1 п.п. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.01.2025</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -243,102 +337,8 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 5.8 п.п. к 01.01.2025</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">↑ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ед. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.01.2025</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">↑ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>19</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ед. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.01.2025</t>
-    </r>
-  </si>
-  <si>
-    <t>210 ед.</t>
-  </si>
-  <si>
-    <t>16.5%</t>
+      <t xml:space="preserve"> 5.7 п.п. к 01.01.2025</t>
+    </r>
   </si>
   <si>
     <r>
@@ -360,7 +360,7 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 11 </t>
+      <t xml:space="preserve"> 7 </t>
     </r>
     <r>
       <rPr>
@@ -820,25 +820,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -848,69 +848,69 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="C2" s="6" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>21</v>
+      <c r="A3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/content/xls/indicators_01.07.2025.xlsx
+++ b/content/xls/indicators_01.07.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFAEB8D-DC02-48C2-B7EF-7BB803A6D300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEEB992-4D6D-4E6B-B9E8-EEF544DA0EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3791" yWindow="7471" windowWidth="23631" windowHeight="8566" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5514" yWindow="8271" windowWidth="23631" windowHeight="8566" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -263,9 +263,6 @@
     <t>210 ед.</t>
   </si>
   <si>
-    <t>16.5%</t>
-  </si>
-  <si>
     <t>Количество банков</t>
   </si>
   <si>
@@ -337,8 +334,32 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 5.7 п.п. к 01.01.2025</t>
-    </r>
+      <t xml:space="preserve"> 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">точ. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>к 01.01.2025</t>
+    </r>
+  </si>
+  <si>
+    <t>16.1%</t>
   </si>
   <si>
     <r>
@@ -360,28 +381,7 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 7 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">точ. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>к 01.01.2025</t>
+      <t xml:space="preserve"> 6.1 п.п. к 01.01.2025</t>
     </r>
   </si>
 </sst>
@@ -389,12 +389,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -500,21 +508,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -823,22 +834,22 @@
         <v>10</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -851,7 +862,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>16</v>
@@ -874,13 +885,13 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>26</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>9</v>

--- a/content/xls/indicators_01.07.2025.xlsx
+++ b/content/xls/indicators_01.07.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEEB992-4D6D-4E6B-B9E8-EEF544DA0EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE277FBA-81C9-4919-82D7-E47B7E534F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5514" yWindow="8271" windowWidth="23631" windowHeight="8566" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -163,9 +163,6 @@
 дистанционного банковского обслуживания</t>
   </si>
   <si>
-    <t>80.9%</t>
-  </si>
-  <si>
     <t>539 ед.</t>
   </si>
   <si>
@@ -383,18 +380,30 @@
       </rPr>
       <t xml:space="preserve"> 6.1 п.п. к 01.01.2025</t>
     </r>
+  </si>
+  <si>
+    <t>80.9%
+Выше среднего</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -508,21 +517,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -530,8 +542,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -834,22 +846,22 @@
         <v>10</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -857,21 +869,21 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:13" ht="29.55" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>3</v>
@@ -885,22 +897,22 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>23</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>24</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>14</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>15</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>7</v>

--- a/content/xls/indicators_01.07.2025.xlsx
+++ b/content/xls/indicators_01.07.2025.xlsx
@@ -1,33 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Юлия\Desktop\ФД_2026\10.08.26\от Егора_итоговые файлы_25.08.26\Ответ_измен. ур.дбо_зеленым\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE277FBA-81C9-4919-82D7-E47B7E534F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5D624E-9D5E-4BCB-8652-D70E4E937A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -359,51 +350,43 @@
     <t>16.1%</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>↓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 6.1 п.п. к 01.01.2025</t>
-    </r>
-  </si>
-  <si>
     <t>80.9%
 Выше среднего</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>↓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 6.1 п.п. к 01.01.2025</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -522,19 +505,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,6 +524,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -826,19 +809,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="14.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.6640625" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" customWidth="1"/>
-    <col min="4" max="4" width="27.77734375" customWidth="1"/>
-    <col min="5" max="5" width="18.77734375" customWidth="1"/>
-    <col min="6" max="6" width="31.109375" customWidth="1"/>
-    <col min="7" max="7" width="24.88671875" customWidth="1"/>
-    <col min="8" max="8" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="31.140625" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" customWidth="1"/>
+    <col min="8" max="8" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="59.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="59.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -869,9 +852,9 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" ht="29.55" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
-        <v>26</v>
+    <row r="2" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>24</v>
@@ -895,17 +878,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>25</v>
+      <c r="B3" s="10" t="s">
+        <v>26</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="10" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -921,17 +904,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
